--- a/Eclarity_TEV_Financials.xlsx
+++ b/Eclarity_TEV_Financials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myntuac-my.sharepoint.com/personal/n1294402_my_ntu_ac_uk/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{8C8464E7-7A4A-452C-930C-349E8742FE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{447F17C1-1518-4495-AD76-294DC55BD340}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{8C8464E7-7A4A-452C-930C-349E8742FE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A983FD14-4AD0-48A8-A114-AF363166189F}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" tabRatio="500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="7" r:id="rId1"/>
@@ -1007,17 +1007,17 @@
     <xf numFmtId="10" fontId="20" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="169" fontId="20" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="14" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="14" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="14" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="14" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3174,408 +3174,409 @@
       <c r="N1" s="93"/>
       <c r="O1" s="93"/>
       <c r="P1" s="93"/>
-      <c r="Q1" s="94"/>
+      <c r="Q1" s="92"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A2" s="94"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="94"/>
-      <c r="O2" s="94"/>
-      <c r="P2" s="94"/>
-      <c r="Q2" s="94"/>
+      <c r="A2" s="92"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A3" s="94"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="94"/>
-      <c r="O3" s="94"/>
-      <c r="P3" s="94"/>
-      <c r="Q3" s="94"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="92"/>
+      <c r="P3" s="92"/>
+      <c r="Q3" s="92"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A4" s="94"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="94"/>
-      <c r="J4" s="94"/>
-      <c r="K4" s="94"/>
-      <c r="L4" s="94"/>
-      <c r="M4" s="94"/>
-      <c r="N4" s="94"/>
-      <c r="O4" s="94"/>
-      <c r="P4" s="94"/>
-      <c r="Q4" s="94"/>
+      <c r="A4" s="92"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="92"/>
+      <c r="L4" s="92"/>
+      <c r="M4" s="92"/>
+      <c r="N4" s="92"/>
+      <c r="O4" s="92"/>
+      <c r="P4" s="92"/>
+      <c r="Q4" s="92"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A5" s="94"/>
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
-      <c r="K5" s="94"/>
-      <c r="L5" s="94"/>
-      <c r="M5" s="94"/>
-      <c r="N5" s="94"/>
-      <c r="O5" s="94"/>
-      <c r="P5" s="94"/>
-      <c r="Q5" s="94"/>
+      <c r="A5" s="92"/>
+      <c r="B5" s="92"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="92"/>
+      <c r="K5" s="92"/>
+      <c r="L5" s="92"/>
+      <c r="M5" s="92"/>
+      <c r="N5" s="92"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="92"/>
+      <c r="Q5" s="92"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A6" s="94"/>
-      <c r="B6" s="94"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="94"/>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="94"/>
-      <c r="K6" s="94"/>
-      <c r="L6" s="94"/>
-      <c r="M6" s="94"/>
-      <c r="N6" s="94"/>
-      <c r="O6" s="94"/>
-      <c r="P6" s="94"/>
-      <c r="Q6" s="94"/>
+      <c r="A6" s="92"/>
+      <c r="B6" s="92"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="92"/>
+      <c r="K6" s="92"/>
+      <c r="L6" s="92"/>
+      <c r="M6" s="92"/>
+      <c r="N6" s="92"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="92"/>
+      <c r="Q6" s="92"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A7" s="94"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="94"/>
-      <c r="L7" s="94"/>
-      <c r="M7" s="94"/>
-      <c r="N7" s="94"/>
-      <c r="O7" s="94"/>
-      <c r="P7" s="94"/>
-      <c r="Q7" s="94"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="92"/>
+      <c r="K7" s="92"/>
+      <c r="L7" s="92"/>
+      <c r="M7" s="92"/>
+      <c r="N7" s="92"/>
+      <c r="O7" s="92"/>
+      <c r="P7" s="92"/>
+      <c r="Q7" s="92"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A8" s="94"/>
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
-      <c r="J8" s="94"/>
-      <c r="K8" s="94"/>
-      <c r="L8" s="94"/>
-      <c r="M8" s="94"/>
-      <c r="N8" s="94"/>
-      <c r="O8" s="94"/>
-      <c r="P8" s="94"/>
-      <c r="Q8" s="94"/>
+      <c r="A8" s="92"/>
+      <c r="B8" s="92"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="92"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="92"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="92"/>
+      <c r="J8" s="92"/>
+      <c r="K8" s="92"/>
+      <c r="L8" s="92"/>
+      <c r="M8" s="92"/>
+      <c r="N8" s="92"/>
+      <c r="O8" s="92"/>
+      <c r="P8" s="92"/>
+      <c r="Q8" s="92"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A9" s="94"/>
-      <c r="B9" s="94"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
-      <c r="J9" s="94"/>
-      <c r="K9" s="94"/>
-      <c r="L9" s="94"/>
-      <c r="M9" s="94"/>
-      <c r="N9" s="94"/>
-      <c r="O9" s="94"/>
-      <c r="P9" s="94"/>
-      <c r="Q9" s="94"/>
+      <c r="A9" s="92"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="92"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="92"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="92"/>
+      <c r="J9" s="92"/>
+      <c r="K9" s="92"/>
+      <c r="L9" s="92"/>
+      <c r="M9" s="92"/>
+      <c r="N9" s="92"/>
+      <c r="O9" s="92"/>
+      <c r="P9" s="92"/>
+      <c r="Q9" s="92"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A10" s="94"/>
-      <c r="B10" s="94"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="94"/>
-      <c r="J10" s="94"/>
-      <c r="K10" s="94"/>
-      <c r="L10" s="94"/>
-      <c r="M10" s="94"/>
-      <c r="N10" s="94"/>
-      <c r="O10" s="94"/>
-      <c r="P10" s="94"/>
-      <c r="Q10" s="94"/>
+      <c r="A10" s="92"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="92"/>
+      <c r="D10" s="92"/>
+      <c r="E10" s="92"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="92"/>
+      <c r="L10" s="92"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="92"/>
+      <c r="O10" s="92"/>
+      <c r="P10" s="92"/>
+      <c r="Q10" s="92"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A11" s="94"/>
-      <c r="B11" s="94"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="94"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="94"/>
-      <c r="J11" s="94"/>
-      <c r="K11" s="94"/>
-      <c r="L11" s="94"/>
-      <c r="M11" s="94"/>
-      <c r="N11" s="94"/>
-      <c r="O11" s="94"/>
-      <c r="P11" s="94"/>
-      <c r="Q11" s="94"/>
+      <c r="A11" s="92"/>
+      <c r="B11" s="92"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="92"/>
+      <c r="J11" s="92"/>
+      <c r="K11" s="92"/>
+      <c r="L11" s="92"/>
+      <c r="M11" s="92"/>
+      <c r="N11" s="92"/>
+      <c r="O11" s="92"/>
+      <c r="P11" s="92"/>
+      <c r="Q11" s="92"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A12" s="94"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="94"/>
-      <c r="K12" s="94"/>
-      <c r="L12" s="94"/>
-      <c r="M12" s="94"/>
-      <c r="N12" s="94"/>
-      <c r="O12" s="94"/>
-      <c r="P12" s="94"/>
-      <c r="Q12" s="94"/>
+      <c r="A12" s="92"/>
+      <c r="B12" s="92"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="92"/>
+      <c r="K12" s="92"/>
+      <c r="L12" s="92"/>
+      <c r="M12" s="92"/>
+      <c r="N12" s="92"/>
+      <c r="O12" s="92"/>
+      <c r="P12" s="92"/>
+      <c r="Q12" s="92"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A13" s="94"/>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="94"/>
-      <c r="L13" s="94"/>
-      <c r="M13" s="94"/>
-      <c r="N13" s="94"/>
-      <c r="O13" s="94"/>
-      <c r="P13" s="94"/>
-      <c r="Q13" s="94"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="92"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="92"/>
+      <c r="H13" s="92"/>
+      <c r="I13" s="92"/>
+      <c r="J13" s="92"/>
+      <c r="K13" s="92"/>
+      <c r="L13" s="92"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="92"/>
+      <c r="O13" s="92"/>
+      <c r="P13" s="92"/>
+      <c r="Q13" s="92"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A14" s="94"/>
-      <c r="B14" s="94"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="94"/>
-      <c r="E14" s="94"/>
-      <c r="F14" s="94"/>
-      <c r="G14" s="94"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="94"/>
-      <c r="K14" s="94"/>
-      <c r="L14" s="94"/>
-      <c r="M14" s="94"/>
-      <c r="N14" s="94"/>
-      <c r="O14" s="94"/>
-      <c r="P14" s="94"/>
-      <c r="Q14" s="94"/>
+      <c r="A14" s="92"/>
+      <c r="B14" s="92"/>
+      <c r="C14" s="92"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="92"/>
+      <c r="F14" s="92"/>
+      <c r="G14" s="92"/>
+      <c r="H14" s="92"/>
+      <c r="I14" s="92"/>
+      <c r="J14" s="92"/>
+      <c r="K14" s="92"/>
+      <c r="L14" s="92"/>
+      <c r="M14" s="92"/>
+      <c r="N14" s="92"/>
+      <c r="O14" s="92"/>
+      <c r="P14" s="92"/>
+      <c r="Q14" s="92"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A15" s="94"/>
-      <c r="B15" s="94"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="94"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="94"/>
-      <c r="K15" s="94"/>
-      <c r="L15" s="94"/>
-      <c r="M15" s="94"/>
-      <c r="N15" s="94"/>
-      <c r="O15" s="94"/>
-      <c r="P15" s="94"/>
-      <c r="Q15" s="94"/>
+      <c r="A15" s="92"/>
+      <c r="B15" s="92"/>
+      <c r="C15" s="92"/>
+      <c r="D15" s="92"/>
+      <c r="E15" s="92"/>
+      <c r="F15" s="92"/>
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
+      <c r="I15" s="92"/>
+      <c r="J15" s="92"/>
+      <c r="K15" s="92"/>
+      <c r="L15" s="92"/>
+      <c r="M15" s="92"/>
+      <c r="N15" s="92"/>
+      <c r="O15" s="92"/>
+      <c r="P15" s="92"/>
+      <c r="Q15" s="92"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A16" s="94"/>
-      <c r="B16" s="94"/>
-      <c r="C16" s="94"/>
-      <c r="D16" s="94"/>
-      <c r="E16" s="94"/>
-      <c r="F16" s="94"/>
-      <c r="G16" s="94"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="94"/>
-      <c r="J16" s="94"/>
-      <c r="K16" s="94"/>
-      <c r="L16" s="94"/>
-      <c r="M16" s="94"/>
-      <c r="N16" s="94"/>
-      <c r="O16" s="94"/>
-      <c r="P16" s="94"/>
-      <c r="Q16" s="94"/>
+      <c r="A16" s="92"/>
+      <c r="B16" s="92"/>
+      <c r="C16" s="92"/>
+      <c r="D16" s="92"/>
+      <c r="E16" s="92"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="92"/>
+      <c r="H16" s="92"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="92"/>
+      <c r="K16" s="92"/>
+      <c r="L16" s="92"/>
+      <c r="M16" s="92"/>
+      <c r="N16" s="92"/>
+      <c r="O16" s="92"/>
+      <c r="P16" s="92"/>
+      <c r="Q16" s="92"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A17" s="94"/>
-      <c r="B17" s="94"/>
-      <c r="C17" s="94"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="94"/>
-      <c r="K17" s="94"/>
-      <c r="L17" s="94"/>
-      <c r="M17" s="94"/>
-      <c r="N17" s="94"/>
-      <c r="O17" s="94"/>
-      <c r="P17" s="94"/>
-      <c r="Q17" s="94"/>
+      <c r="A17" s="92"/>
+      <c r="B17" s="92"/>
+      <c r="C17" s="92"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="92"/>
+      <c r="F17" s="92"/>
+      <c r="G17" s="92"/>
+      <c r="H17" s="92"/>
+      <c r="I17" s="92"/>
+      <c r="J17" s="92"/>
+      <c r="K17" s="92"/>
+      <c r="L17" s="92"/>
+      <c r="M17" s="92"/>
+      <c r="N17" s="92"/>
+      <c r="O17" s="92"/>
+      <c r="P17" s="92"/>
+      <c r="Q17" s="92"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A18" s="94"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="94"/>
-      <c r="E18" s="94"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="94"/>
-      <c r="K18" s="94"/>
-      <c r="L18" s="94"/>
-      <c r="M18" s="94"/>
-      <c r="N18" s="94"/>
-      <c r="O18" s="94"/>
-      <c r="P18" s="94"/>
-      <c r="Q18" s="94"/>
+      <c r="A18" s="92"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="92"/>
+      <c r="G18" s="92"/>
+      <c r="H18" s="92"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="92"/>
+      <c r="K18" s="92"/>
+      <c r="L18" s="92"/>
+      <c r="M18" s="92"/>
+      <c r="N18" s="92"/>
+      <c r="O18" s="92"/>
+      <c r="P18" s="92"/>
+      <c r="Q18" s="92"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A19" s="94"/>
-      <c r="B19" s="94"/>
-      <c r="C19" s="94"/>
-      <c r="D19" s="94"/>
-      <c r="E19" s="94"/>
-      <c r="F19" s="94"/>
-      <c r="G19" s="94"/>
-      <c r="H19" s="94"/>
-      <c r="I19" s="94"/>
-      <c r="J19" s="94"/>
-      <c r="K19" s="94"/>
-      <c r="L19" s="94"/>
-      <c r="M19" s="94"/>
-      <c r="N19" s="94"/>
-      <c r="O19" s="94"/>
-      <c r="P19" s="94"/>
-      <c r="Q19" s="94"/>
+      <c r="A19" s="92"/>
+      <c r="B19" s="92"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="92"/>
+      <c r="G19" s="92"/>
+      <c r="H19" s="92"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="92"/>
+      <c r="K19" s="92"/>
+      <c r="L19" s="92"/>
+      <c r="M19" s="92"/>
+      <c r="N19" s="92"/>
+      <c r="O19" s="92"/>
+      <c r="P19" s="92"/>
+      <c r="Q19" s="92"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A20" s="94"/>
-      <c r="B20" s="94"/>
-      <c r="C20" s="94"/>
-      <c r="D20" s="94"/>
-      <c r="E20" s="94"/>
-      <c r="F20" s="94"/>
-      <c r="G20" s="94"/>
-      <c r="H20" s="94"/>
-      <c r="I20" s="94"/>
-      <c r="J20" s="94"/>
-      <c r="K20" s="94"/>
-      <c r="L20" s="94"/>
-      <c r="M20" s="94"/>
-      <c r="N20" s="94"/>
-      <c r="O20" s="94"/>
-      <c r="P20" s="94"/>
-      <c r="Q20" s="94"/>
+      <c r="A20" s="92"/>
+      <c r="B20" s="92"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="92"/>
+      <c r="F20" s="92"/>
+      <c r="G20" s="92"/>
+      <c r="H20" s="92"/>
+      <c r="I20" s="92"/>
+      <c r="J20" s="92"/>
+      <c r="K20" s="92"/>
+      <c r="L20" s="92"/>
+      <c r="M20" s="92"/>
+      <c r="N20" s="92"/>
+      <c r="O20" s="92"/>
+      <c r="P20" s="92"/>
+      <c r="Q20" s="92"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A21" s="94"/>
-      <c r="B21" s="94"/>
-      <c r="C21" s="94"/>
-      <c r="D21" s="94"/>
-      <c r="E21" s="94"/>
-      <c r="F21" s="94"/>
-      <c r="G21" s="94"/>
-      <c r="H21" s="94"/>
-      <c r="I21" s="94"/>
-      <c r="J21" s="94"/>
-      <c r="K21" s="94"/>
-      <c r="L21" s="94"/>
-      <c r="M21" s="94"/>
-      <c r="N21" s="94"/>
-      <c r="O21" s="94"/>
-      <c r="P21" s="94"/>
-      <c r="Q21" s="94"/>
+      <c r="A21" s="92"/>
+      <c r="B21" s="92"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="92"/>
+      <c r="G21" s="92"/>
+      <c r="H21" s="92"/>
+      <c r="I21" s="92"/>
+      <c r="J21" s="92"/>
+      <c r="K21" s="92"/>
+      <c r="L21" s="92"/>
+      <c r="M21" s="92"/>
+      <c r="N21" s="92"/>
+      <c r="O21" s="92"/>
+      <c r="P21" s="92"/>
+      <c r="Q21" s="92"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A22" s="94"/>
-      <c r="B22" s="94"/>
-      <c r="C22" s="94"/>
-      <c r="D22" s="94"/>
-      <c r="E22" s="94"/>
-      <c r="F22" s="94"/>
-      <c r="G22" s="94"/>
-      <c r="H22" s="94"/>
-      <c r="I22" s="94"/>
-      <c r="J22" s="94"/>
-      <c r="K22" s="94"/>
-      <c r="L22" s="94"/>
-      <c r="M22" s="94"/>
-      <c r="N22" s="94"/>
-      <c r="O22" s="94"/>
-      <c r="P22" s="94"/>
-      <c r="Q22" s="94"/>
+      <c r="A22" s="92"/>
+      <c r="B22" s="92"/>
+      <c r="C22" s="92"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="92"/>
+      <c r="H22" s="92"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="92"/>
+      <c r="K22" s="92"/>
+      <c r="L22" s="92"/>
+      <c r="M22" s="92"/>
+      <c r="N22" s="92"/>
+      <c r="O22" s="92"/>
+      <c r="P22" s="92"/>
+      <c r="Q22" s="92"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="TljhjIXW4YXrFWw76IAX2zUk9prxXF0ldMFAhlzm9WOpzprEB5cA+85PVgbxoEuAcWbHVgESl4xnnN+vH1V2wA==" saltValue="OCS9lq5YHE8bYA6nem7oWQ==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -3596,19 +3597,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="1.35">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
     </row>
     <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
@@ -4298,6 +4299,7 @@
       <c r="G30" s="14"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
@@ -4320,19 +4322,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="1.35">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
     </row>
     <row r="2" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
@@ -5224,6 +5226,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
@@ -5246,19 +5249,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="1.35">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
     </row>
     <row r="2" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
@@ -6080,6 +6083,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
@@ -6100,19 +6104,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="1.35">
-      <c r="B1" s="88" t="s">
+      <c r="B1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
     </row>
     <row r="2" spans="2:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1"/>
@@ -6196,15 +6200,15 @@
       <c r="B7" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="90">
+      <c r="D7" s="89">
         <f>'Cash Flow Statement'!D9</f>
         <v>0</v>
       </c>
-      <c r="E7" s="90">
+      <c r="E7" s="89">
         <f>'Cash Flow Statement'!E9</f>
         <v>0</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="89">
         <f>'Cash Flow Statement'!F9</f>
         <v>0</v>
       </c>
@@ -6233,9 +6237,9 @@
       <c r="B8" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="91"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="91"/>
+      <c r="D8" s="90"/>
+      <c r="E8" s="90"/>
+      <c r="F8" s="90"/>
       <c r="G8" s="35">
         <v>7.0000000000000001E-3</v>
       </c>
@@ -6256,9 +6260,9 @@
       <c r="B10" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="92"/>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
       <c r="G10" s="6">
         <f>F13</f>
         <v>1575898</v>
@@ -6284,9 +6288,9 @@
       <c r="B11" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="92"/>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="91"/>
       <c r="G11" s="22">
         <f>G12+(F17-G17)</f>
         <v>285497.06870069844</v>
@@ -6312,9 +6316,9 @@
       <c r="B12" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="92"/>
-      <c r="E12" s="92"/>
-      <c r="F12" s="92"/>
+      <c r="D12" s="91"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
       <c r="G12" s="6">
         <f>G7</f>
         <v>283319.34813</v>
@@ -6422,6 +6426,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="1">
     <mergeCell ref="B1:L1"/>
   </mergeCells>
@@ -6443,19 +6448,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="45.75" customHeight="1" x14ac:dyDescent="1.35">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
     </row>
     <row r="2" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
@@ -6966,6 +6971,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
@@ -6985,19 +6991,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="46.15" x14ac:dyDescent="1.35">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="89"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B2" s="26"/>
@@ -7059,6 +7065,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
